--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-dicom-sop-instance-observation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$159</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4598" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4947" uniqueCount="455">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -532,6 +532,132 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-sop-class-cisis</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -540,10 +666,6 @@
   </si>
   <si>
     <t>Observation.text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
   </si>
   <si>
     <t xml:space="preserve"> url permettant d’accéder aux images sur la Drim box source. Cette url, basée sur le profil IHE Invoke Image Display , est construite de la manière suivante :https://&lt;location&gt;/IHEInvokeImageDisplay?requestType=STUDY&amp;amp;studyUID=&lt;StudyInstanceUID&gt;&amp;amp;Accessionnumber=&lt;Accessionnumber&gt;&amp;amp;idCDA=&lt;idCDA&gt; avec les paramètres :&lt;location&gt; : Racine de l’URL par laquelle on accède au PACS qui met à disposition de l’examen (cf volet CI-SIS_SPEC_TECH_Objet ref d'examens d'imagerie)&lt;StudyInstanceUID&gt; : Identifiant de l’examen attribué par le RIS&lt;Accessionnumber&gt; : Identifiant de la demande attribué par le RIS (concaténer root.extension)&lt;idCDA&gt; : Identifiant du document CDA IMG-CR-IMG (élément &lt;id root&gt;)</t>
@@ -1622,7 +1744,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK148"/>
+  <dimension ref="A1:AK159"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="86.6171875" customWidth="true" bestFit="true"/>
@@ -4323,7 +4445,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>160</v>
       </c>
@@ -4342,7 +4464,7 @@
         <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4637,7 +4759,9 @@
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4654,10 +4778,12 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4683,13 +4809,11 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -4707,7 +4831,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>168</v>
+        <v>89</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4727,18 +4851,20 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
@@ -4753,13 +4879,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4810,7 +4934,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4828,28 +4952,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>84</v>
+        <v>173</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>74</v>
@@ -4858,11 +4982,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>86</v>
+        <v>174</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4889,11 +5013,13 @@
         <v>74</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4911,7 +5037,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>89</v>
+        <v>175</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4931,17 +5057,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4959,11 +5085,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4990,11 +5116,13 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -5060,11 +5188,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5115,37 +5243,37 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="AG34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>80</v>
@@ -5154,7 +5282,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -5163,11 +5291,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5194,11 +5322,13 @@
         <v>74</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -5216,7 +5346,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5236,18 +5366,16 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" t="s" s="2">
-        <v>191</v>
-      </c>
+      <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5264,11 +5392,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5319,7 +5447,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5339,18 +5467,16 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" t="s" s="2">
-        <v>195</v>
-      </c>
+      <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5367,11 +5493,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5383,7 +5509,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5398,11 +5524,13 @@
         <v>74</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>199</v>
+        <v>74</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -5420,7 +5548,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5440,16 +5568,18 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5466,10 +5596,12 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>197</v>
       </c>
       <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
+      <c r="M38" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5495,11 +5627,13 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>202</v>
+        <v>74</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5517,7 +5651,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5537,21 +5671,23 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
@@ -5563,17 +5699,13 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
@@ -5622,13 +5754,13 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
@@ -5642,23 +5774,23 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
@@ -5670,13 +5802,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5727,13 +5857,13 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
@@ -5747,18 +5877,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" t="s" s="2">
-        <v>215</v>
-      </c>
+      <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
@@ -5775,12 +5903,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="L41" s="2"/>
-      <c r="M41" t="s" s="2">
-        <v>216</v>
-      </c>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5830,7 +5956,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5848,12 +5974,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5867,7 +5993,7 @@
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5876,10 +6002,14 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5905,11 +6035,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>219</v>
+        <v>74</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5927,7 +6059,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5945,18 +6077,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
@@ -5964,7 +6098,7 @@
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5973,13 +6107,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>222</v>
+        <v>86</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6006,13 +6138,11 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -6030,7 +6160,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>220</v>
+        <v>89</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6050,16 +6180,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
@@ -6076,10 +6208,12 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>224</v>
+        <v>85</v>
       </c>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6105,11 +6239,11 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>198</v>
+        <v>87</v>
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -6127,7 +6261,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6147,16 +6281,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
@@ -6173,10 +6309,12 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
+      <c r="M45" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6226,7 +6364,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6246,16 +6384,18 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E46" s="2"/>
+      <c r="E46" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
@@ -6272,10 +6412,12 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
+      <c r="M46" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6305,25 +6447,25 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6352,12 +6494,14 @@
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" s="2"/>
+      <c r="E47" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>74</v>
@@ -6369,10 +6513,12 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>231</v>
+        <v>85</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
+      <c r="M47" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6422,13 +6568,13 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>74</v>
@@ -6442,21 +6588,23 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" s="2"/>
+      <c r="E48" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>74</v>
@@ -6468,10 +6616,12 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>224</v>
+        <v>85</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
+      <c r="M48" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6482,7 +6632,7 @@
         <v>74</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>74</v>
+        <v>237</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>74</v>
@@ -6497,11 +6647,11 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>87</v>
+        <v>238</v>
       </c>
       <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6519,13 +6669,13 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>74</v>
@@ -6539,10 +6689,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6553,7 +6703,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -6565,7 +6715,7 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>224</v>
+        <v>85</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6594,11 +6744,11 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>198</v>
+        <v>87</v>
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6616,13 +6766,13 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>74</v>
@@ -6636,10 +6786,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6650,7 +6800,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>74</v>
@@ -6662,13 +6812,17 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L50" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="M50" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>74</v>
@@ -6717,13 +6871,13 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>74</v>
@@ -6737,18 +6891,20 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>75</v>
@@ -6763,10 +6919,14 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -6816,7 +6976,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6836,21 +6996,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E52" s="2"/>
+      <c r="E52" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -6862,10 +7024,12 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>241</v>
+        <v>197</v>
       </c>
       <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
+      <c r="M52" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -6915,13 +7079,13 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>74</v>
@@ -6935,10 +7099,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6949,7 +7113,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -6961,7 +7125,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>243</v>
+        <v>91</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6990,13 +7154,11 @@
         <v>74</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>74</v>
+        <v>259</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>74</v>
@@ -7014,13 +7176,13 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>74</v>
@@ -7032,12 +7194,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7048,10 +7210,10 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>74</v>
@@ -7060,10 +7222,14 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7113,13 +7279,13 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>74</v>
@@ -7133,10 +7299,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7147,7 +7313,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>74</v>
@@ -7159,7 +7325,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -7188,13 +7354,11 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>74</v>
+        <v>265</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7212,13 +7376,13 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>74</v>
@@ -7232,10 +7396,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7246,7 +7410,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>74</v>
@@ -7258,7 +7422,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7311,13 +7475,13 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>74</v>
@@ -7331,10 +7495,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7345,10 +7509,10 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>74</v>
@@ -7357,7 +7521,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>251</v>
+        <v>91</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7386,35 +7550,35 @@
         <v>74</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>74</v>
@@ -7428,14 +7592,12 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
@@ -7456,11 +7618,9 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7511,7 +7671,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7531,23 +7691,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>74</v>
@@ -7559,12 +7717,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>85</v>
+        <v>264</v>
       </c>
       <c r="L59" s="2"/>
-      <c r="M59" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M59" s="2"/>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7594,7 +7750,7 @@
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>88</v>
+        <v>273</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7612,13 +7768,13 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>89</v>
+        <v>272</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>74</v>
@@ -7632,10 +7788,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7658,12 +7814,10 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>91</v>
+        <v>264</v>
       </c>
       <c r="L60" s="2"/>
-      <c r="M60" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M60" s="2"/>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -7689,13 +7843,11 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>74</v>
+        <v>275</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7713,7 +7865,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>93</v>
+        <v>274</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7733,10 +7885,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7747,7 +7899,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>74</v>
@@ -7759,11 +7911,11 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>96</v>
+        <v>277</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7814,19 +7966,19 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>97</v>
+        <v>276</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>74</v>
@@ -7834,18 +7986,16 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E62" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
@@ -7862,12 +8012,10 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>85</v>
+        <v>279</v>
       </c>
       <c r="L62" s="2"/>
-      <c r="M62" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M62" s="2"/>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7893,11 +8041,13 @@
         <v>74</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>74</v>
@@ -7915,7 +8065,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>89</v>
+        <v>278</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7935,23 +8085,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E63" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>74</v>
@@ -7963,12 +8111,10 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>102</v>
+        <v>281</v>
       </c>
       <c r="L63" s="2"/>
-      <c r="M63" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8018,13 +8164,13 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>104</v>
+        <v>280</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>74</v>
@@ -8038,23 +8184,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E64" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>74</v>
@@ -8066,12 +8210,10 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>107</v>
+        <v>283</v>
       </c>
       <c r="L64" s="2"/>
-      <c r="M64" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8121,13 +8263,13 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>109</v>
+        <v>282</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>74</v>
@@ -8141,23 +8283,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E65" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>74</v>
@@ -8169,12 +8309,10 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>112</v>
+        <v>285</v>
       </c>
       <c r="L65" s="2"/>
-      <c r="M65" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8182,7 +8320,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -8224,13 +8362,13 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>115</v>
+        <v>284</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>74</v>
@@ -8244,23 +8382,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E66" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -8272,12 +8408,10 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>102</v>
+        <v>287</v>
       </c>
       <c r="L66" s="2"/>
-      <c r="M66" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8327,13 +8461,13 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>119</v>
+        <v>286</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>74</v>
@@ -8347,10 +8481,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8373,12 +8507,10 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>95</v>
+        <v>289</v>
       </c>
       <c r="L67" s="2"/>
-      <c r="M67" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8428,7 +8560,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>125</v>
+        <v>288</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8448,10 +8580,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8459,13 +8591,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>74</v>
@@ -8474,7 +8606,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>85</v>
+        <v>291</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8488,7 +8620,7 @@
         <v>74</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>276</v>
+        <v>74</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>74</v>
@@ -8503,35 +8635,35 @@
         <v>74</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>277</v>
+        <v>74</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>74</v>
@@ -8545,12 +8677,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
@@ -8559,7 +8693,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -8571,12 +8705,12 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L69" s="2"/>
-      <c r="M69" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8626,13 +8760,13 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>74</v>
@@ -8646,16 +8780,18 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E70" s="2"/>
+      <c r="E70" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
@@ -8672,16 +8808,16 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>285</v>
+        <v>86</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
-        <v>286</v>
+        <v>74</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
@@ -8703,13 +8839,11 @@
         <v>74</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -8727,7 +8861,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>287</v>
+        <v>89</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8747,10 +8881,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8761,7 +8895,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>74</v>
@@ -8773,10 +8907,12 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
+      <c r="M71" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8826,13 +8962,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>290</v>
+        <v>93</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8846,10 +8982,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8872,10 +9008,12 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>293</v>
+        <v>95</v>
       </c>
       <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
+      <c r="M72" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -8925,7 +9063,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>294</v>
+        <v>97</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8937,7 +9075,7 @@
         <v>74</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>74</v>
@@ -8945,16 +9083,18 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E73" s="2"/>
+      <c r="E73" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
@@ -8971,10 +9111,12 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>297</v>
+        <v>85</v>
       </c>
       <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
+      <c r="M73" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9000,13 +9142,11 @@
         <v>74</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>74</v>
@@ -9024,7 +9164,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>298</v>
+        <v>89</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9044,16 +9184,18 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" s="2"/>
+      <c r="E74" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
@@ -9070,10 +9212,12 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>301</v>
+        <v>102</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
+      <c r="M74" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9123,7 +9267,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>302</v>
+        <v>104</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9143,16 +9287,18 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
@@ -9169,10 +9315,12 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>305</v>
+        <v>107</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9222,7 +9370,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>306</v>
+        <v>109</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9242,18 +9390,20 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E76" s="2"/>
+      <c r="E76" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>75</v>
@@ -9268,10 +9418,12 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>309</v>
+        <v>112</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
+      <c r="M76" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9279,7 +9431,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>74</v>
@@ -9321,7 +9473,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>310</v>
+        <v>115</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9341,18 +9493,20 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E77" s="2"/>
+      <c r="E77" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>75</v>
@@ -9367,10 +9521,12 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>313</v>
+        <v>102</v>
       </c>
       <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
+      <c r="M77" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9420,7 +9576,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>314</v>
+        <v>119</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9440,10 +9596,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9454,7 +9610,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -9466,10 +9622,12 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>317</v>
+        <v>95</v>
       </c>
       <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
+      <c r="M78" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9519,13 +9677,13 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>318</v>
+        <v>125</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
@@ -9539,10 +9697,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9550,7 +9708,7 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>75</v>
@@ -9565,7 +9723,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>321</v>
+        <v>85</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9579,7 +9737,7 @@
         <v>74</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>74</v>
+        <v>316</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>74</v>
@@ -9594,13 +9752,11 @@
         <v>74</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>74</v>
+        <v>317</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9618,10 +9774,10 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>75</v>
@@ -9638,10 +9794,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9664,10 +9820,12 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9717,7 +9875,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9737,10 +9895,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9763,14 +9921,16 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
+      <c r="M81" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
-        <v>74</v>
+        <v>326</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
@@ -9816,7 +9976,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9836,10 +9996,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9862,7 +10022,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9915,7 +10075,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9935,14 +10095,12 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
@@ -9963,11 +10121,9 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10018,13 +10174,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>250</v>
+        <v>334</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -10038,18 +10194,16 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>257</v>
+        <v>336</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E84" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
@@ -10066,12 +10220,10 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>85</v>
+        <v>337</v>
       </c>
       <c r="L84" s="2"/>
-      <c r="M84" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10097,11 +10249,13 @@
         <v>74</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>74</v>
@@ -10119,7 +10273,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>89</v>
+        <v>338</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10139,10 +10293,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10153,7 +10307,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -10165,12 +10319,10 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>91</v>
+        <v>341</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10220,13 +10372,13 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>93</v>
+        <v>342</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
@@ -10240,10 +10392,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>261</v>
+        <v>344</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10266,12 +10418,10 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>95</v>
+        <v>345</v>
       </c>
       <c r="L86" s="2"/>
-      <c r="M86" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10321,7 +10471,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>97</v>
+        <v>346</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10333,7 +10483,7 @@
         <v>74</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>74</v>
@@ -10341,18 +10491,16 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>263</v>
+        <v>348</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E87" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
@@ -10369,12 +10517,10 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>85</v>
+        <v>349</v>
       </c>
       <c r="L87" s="2"/>
-      <c r="M87" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M87" s="2"/>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10400,11 +10546,13 @@
         <v>74</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>74</v>
@@ -10422,7 +10570,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>89</v>
+        <v>350</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10442,18 +10590,16 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>265</v>
+        <v>352</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E88" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
@@ -10470,12 +10616,10 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>102</v>
+        <v>353</v>
       </c>
       <c r="L88" s="2"/>
-      <c r="M88" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10525,7 +10669,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>104</v>
+        <v>354</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10545,18 +10689,16 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>267</v>
+        <v>356</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E89" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
@@ -10573,12 +10715,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>107</v>
+        <v>357</v>
       </c>
       <c r="L89" s="2"/>
-      <c r="M89" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10628,7 +10768,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>109</v>
+        <v>358</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10648,20 +10788,18 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>269</v>
+        <v>360</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E90" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>75</v>
@@ -10676,12 +10814,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>112</v>
+        <v>361</v>
       </c>
       <c r="L90" s="2"/>
-      <c r="M90" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -10689,7 +10825,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>74</v>
@@ -10731,7 +10867,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>115</v>
+        <v>362</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10751,20 +10887,18 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>271</v>
+        <v>364</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E91" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>75</v>
@@ -10779,12 +10913,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>102</v>
+        <v>365</v>
       </c>
       <c r="L91" s="2"/>
-      <c r="M91" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -10834,7 +10966,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>119</v>
+        <v>366</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10854,10 +10986,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>273</v>
+        <v>368</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10868,7 +11000,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>74</v>
@@ -10880,12 +11012,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>95</v>
+        <v>369</v>
       </c>
       <c r="L92" s="2"/>
-      <c r="M92" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -10935,13 +11065,13 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>125</v>
+        <v>370</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>74</v>
@@ -10955,10 +11085,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>275</v>
+        <v>372</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10966,7 +11096,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>75</v>
@@ -10981,7 +11111,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>85</v>
+        <v>373</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -11010,11 +11140,13 @@
         <v>74</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y93" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z93" t="s" s="2">
-        <v>277</v>
+        <v>74</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>74</v>
@@ -11032,10 +11164,10 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>278</v>
+        <v>374</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>75</v>
@@ -11052,12 +11184,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
@@ -11078,12 +11212,12 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L94" s="2"/>
-      <c r="M94" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M94" s="2"/>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11133,13 +11267,13 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>74</v>
@@ -11153,16 +11287,18 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E95" s="2"/>
+      <c r="E95" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
@@ -11179,16 +11315,16 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>285</v>
+        <v>86</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
-        <v>286</v>
+        <v>74</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
@@ -11210,13 +11346,11 @@
         <v>74</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>74</v>
@@ -11234,7 +11368,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>287</v>
+        <v>89</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11254,10 +11388,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11268,7 +11402,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>74</v>
@@ -11280,10 +11414,12 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
+      <c r="M96" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11333,13 +11469,13 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>290</v>
+        <v>93</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>74</v>
@@ -11353,10 +11489,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11379,10 +11515,12 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>293</v>
+        <v>95</v>
       </c>
       <c r="L97" s="2"/>
-      <c r="M97" s="2"/>
+      <c r="M97" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -11432,7 +11570,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>294</v>
+        <v>97</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11444,7 +11582,7 @@
         <v>74</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>74</v>
@@ -11452,16 +11590,18 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
@@ -11478,10 +11618,12 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>297</v>
+        <v>85</v>
       </c>
       <c r="L98" s="2"/>
-      <c r="M98" s="2"/>
+      <c r="M98" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11507,13 +11649,11 @@
         <v>74</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>74</v>
@@ -11531,7 +11671,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>298</v>
+        <v>89</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11551,16 +11691,18 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
@@ -11577,10 +11719,12 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>301</v>
+        <v>102</v>
       </c>
       <c r="L99" s="2"/>
-      <c r="M99" s="2"/>
+      <c r="M99" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -11630,7 +11774,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>302</v>
+        <v>104</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -11650,16 +11794,18 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
@@ -11676,10 +11822,12 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>305</v>
+        <v>107</v>
       </c>
       <c r="L100" s="2"/>
-      <c r="M100" s="2"/>
+      <c r="M100" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -11729,7 +11877,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>306</v>
+        <v>109</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11749,18 +11897,20 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F101" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>75</v>
@@ -11775,10 +11925,12 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>355</v>
+        <v>112</v>
       </c>
       <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
+      <c r="M101" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -11786,7 +11938,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>74</v>
@@ -11828,7 +11980,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>310</v>
+        <v>115</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11848,18 +12000,20 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E102" s="2"/>
+      <c r="E102" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>75</v>
@@ -11874,10 +12028,12 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>313</v>
+        <v>102</v>
       </c>
       <c r="L102" s="2"/>
-      <c r="M102" s="2"/>
+      <c r="M102" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -11927,7 +12083,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>314</v>
+        <v>119</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -11947,10 +12103,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11961,7 +12117,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>74</v>
@@ -11973,10 +12129,12 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>317</v>
+        <v>95</v>
       </c>
       <c r="L103" s="2"/>
-      <c r="M103" s="2"/>
+      <c r="M103" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -12026,13 +12184,13 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>318</v>
+        <v>125</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>74</v>
@@ -12046,10 +12204,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12057,7 +12215,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>75</v>
@@ -12072,7 +12230,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>321</v>
+        <v>85</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12101,13 +12259,11 @@
         <v>74</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>74</v>
+        <v>317</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>74</v>
@@ -12125,10 +12281,10 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>75</v>
@@ -12145,10 +12301,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12171,10 +12327,12 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="L105" s="2"/>
-      <c r="M105" s="2"/>
+      <c r="M105" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -12224,7 +12382,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12244,10 +12402,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12270,14 +12428,16 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="L106" s="2"/>
-      <c r="M106" s="2"/>
+      <c r="M106" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
-        <v>74</v>
+        <v>326</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
@@ -12323,7 +12483,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12343,10 +12503,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12369,7 +12529,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12422,7 +12582,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12442,14 +12602,12 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>74</v>
       </c>
@@ -12470,11 +12628,9 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12525,13 +12681,13 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>250</v>
+        <v>334</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>74</v>
@@ -12545,18 +12701,16 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>257</v>
+        <v>336</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E109" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
@@ -12573,12 +12727,10 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>85</v>
+        <v>337</v>
       </c>
       <c r="L109" s="2"/>
-      <c r="M109" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M109" s="2"/>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -12604,11 +12756,13 @@
         <v>74</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y109" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z109" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>74</v>
@@ -12626,7 +12780,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>89</v>
+        <v>338</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12646,10 +12800,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>259</v>
+        <v>340</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12660,7 +12814,7 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>74</v>
@@ -12672,12 +12826,10 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>91</v>
+        <v>341</v>
       </c>
       <c r="L110" s="2"/>
-      <c r="M110" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -12727,13 +12879,13 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>93</v>
+        <v>342</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>74</v>
@@ -12747,10 +12899,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>261</v>
+        <v>344</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12773,12 +12925,10 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>95</v>
+        <v>345</v>
       </c>
       <c r="L111" s="2"/>
-      <c r="M111" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -12828,7 +12978,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>97</v>
+        <v>346</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12840,7 +12990,7 @@
         <v>74</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>74</v>
@@ -12848,18 +12998,16 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>263</v>
+        <v>348</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E112" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
@@ -12876,12 +13024,10 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="L112" s="2"/>
-      <c r="M112" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -12907,11 +13053,13 @@
         <v>74</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>74</v>
@@ -12929,7 +13077,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>89</v>
+        <v>350</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12949,18 +13097,16 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>265</v>
+        <v>352</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E113" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>80</v>
       </c>
@@ -12977,12 +13123,10 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>102</v>
+        <v>353</v>
       </c>
       <c r="L113" s="2"/>
-      <c r="M113" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13032,7 +13176,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>104</v>
+        <v>354</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13052,18 +13196,16 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>267</v>
+        <v>356</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E114" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
@@ -13080,12 +13222,10 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>107</v>
+        <v>357</v>
       </c>
       <c r="L114" s="2"/>
-      <c r="M114" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13135,7 +13275,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>109</v>
+        <v>358</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13155,20 +13295,18 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>269</v>
+        <v>360</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E115" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>75</v>
@@ -13183,12 +13321,10 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>112</v>
+        <v>361</v>
       </c>
       <c r="L115" s="2"/>
-      <c r="M115" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13196,7 +13332,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>74</v>
@@ -13238,7 +13374,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>115</v>
+        <v>362</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13258,20 +13394,18 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>271</v>
+        <v>364</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E116" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>75</v>
@@ -13286,12 +13420,10 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>102</v>
+        <v>365</v>
       </c>
       <c r="L116" s="2"/>
-      <c r="M116" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M116" s="2"/>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -13341,7 +13473,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>119</v>
+        <v>366</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13361,10 +13493,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>273</v>
+        <v>368</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13375,7 +13507,7 @@
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>74</v>
@@ -13387,12 +13519,10 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>95</v>
+        <v>369</v>
       </c>
       <c r="L117" s="2"/>
-      <c r="M117" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M117" s="2"/>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -13442,13 +13572,13 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>125</v>
+        <v>370</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>74</v>
@@ -13462,10 +13592,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>275</v>
+        <v>372</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13473,7 +13603,7 @@
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
         <v>75</v>
@@ -13488,7 +13618,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>85</v>
+        <v>373</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -13502,47 +13632,49 @@
         <v>74</v>
       </c>
       <c r="S118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF118" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="T118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y118" s="2"/>
-      <c r="Z118" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="AG118" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>75</v>
@@ -13559,12 +13691,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C119" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="D119" t="s" s="2">
         <v>74</v>
       </c>
@@ -13585,12 +13719,12 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L119" s="2"/>
-      <c r="M119" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -13640,13 +13774,13 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>74</v>
@@ -13660,16 +13794,18 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E120" s="2"/>
+      <c r="E120" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F120" t="s" s="2">
         <v>80</v>
       </c>
@@ -13686,16 +13822,16 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" t="s" s="2">
-        <v>285</v>
+        <v>86</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
-        <v>286</v>
+        <v>74</v>
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
@@ -13717,13 +13853,11 @@
         <v>74</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>74</v>
@@ -13741,7 +13875,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>287</v>
+        <v>89</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -13761,10 +13895,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13775,7 +13909,7 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>74</v>
@@ -13787,10 +13921,12 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L121" s="2"/>
-      <c r="M121" s="2"/>
+      <c r="M121" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -13840,13 +13976,13 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>290</v>
+        <v>93</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>74</v>
@@ -13860,10 +13996,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13886,10 +14022,12 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>293</v>
+        <v>95</v>
       </c>
       <c r="L122" s="2"/>
-      <c r="M122" s="2"/>
+      <c r="M122" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -13939,7 +14077,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>294</v>
+        <v>97</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -13951,7 +14089,7 @@
         <v>74</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>74</v>
@@ -13959,16 +14097,18 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E123" s="2"/>
+      <c r="E123" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F123" t="s" s="2">
         <v>80</v>
       </c>
@@ -13985,10 +14125,12 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>297</v>
+        <v>85</v>
       </c>
       <c r="L123" s="2"/>
-      <c r="M123" s="2"/>
+      <c r="M123" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -14014,13 +14156,11 @@
         <v>74</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>74</v>
@@ -14038,7 +14178,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>298</v>
+        <v>89</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14058,16 +14198,18 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E124" s="2"/>
+      <c r="E124" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F124" t="s" s="2">
         <v>80</v>
       </c>
@@ -14084,10 +14226,12 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>301</v>
+        <v>102</v>
       </c>
       <c r="L124" s="2"/>
-      <c r="M124" s="2"/>
+      <c r="M124" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -14137,7 +14281,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>302</v>
+        <v>104</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14157,16 +14301,18 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E125" s="2"/>
+      <c r="E125" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F125" t="s" s="2">
         <v>80</v>
       </c>
@@ -14183,10 +14329,12 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>305</v>
+        <v>107</v>
       </c>
       <c r="L125" s="2"/>
-      <c r="M125" s="2"/>
+      <c r="M125" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -14236,7 +14384,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>306</v>
+        <v>109</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14256,18 +14404,20 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E126" s="2"/>
+      <c r="E126" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F126" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>75</v>
@@ -14282,10 +14432,12 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>383</v>
+        <v>112</v>
       </c>
       <c r="L126" s="2"/>
-      <c r="M126" s="2"/>
+      <c r="M126" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -14293,7 +14445,7 @@
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>74</v>
@@ -14335,7 +14487,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>310</v>
+        <v>115</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14355,18 +14507,20 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E127" s="2"/>
+      <c r="E127" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F127" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>75</v>
@@ -14381,10 +14535,12 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>313</v>
+        <v>102</v>
       </c>
       <c r="L127" s="2"/>
-      <c r="M127" s="2"/>
+      <c r="M127" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -14434,7 +14590,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>314</v>
+        <v>119</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14454,10 +14610,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14468,7 +14624,7 @@
         <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>74</v>
@@ -14480,10 +14636,12 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>317</v>
+        <v>95</v>
       </c>
       <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
+      <c r="M128" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -14533,13 +14691,13 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>318</v>
+        <v>125</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>74</v>
@@ -14553,10 +14711,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14564,7 +14722,7 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>75</v>
@@ -14579,7 +14737,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>321</v>
+        <v>85</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -14593,7 +14751,7 @@
         <v>74</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>74</v>
+        <v>414</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>74</v>
@@ -14608,13 +14766,11 @@
         <v>74</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>74</v>
+        <v>317</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>74</v>
@@ -14632,10 +14788,10 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>75</v>
@@ -14652,10 +14808,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14678,10 +14834,12 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>325</v>
+        <v>107</v>
       </c>
       <c r="L130" s="2"/>
-      <c r="M130" s="2"/>
+      <c r="M130" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -14731,7 +14889,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14751,10 +14909,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14777,14 +14935,16 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="L131" s="2"/>
-      <c r="M131" s="2"/>
+      <c r="M131" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
-        <v>74</v>
+        <v>326</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
@@ -14830,7 +14990,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -14850,10 +15010,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -14876,7 +15036,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -14929,7 +15089,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -14949,10 +15109,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>390</v>
+        <v>332</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -14963,7 +15123,7 @@
         <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>74</v>
@@ -14975,7 +15135,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>391</v>
+        <v>333</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15028,13 +15188,13 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>390</v>
+        <v>334</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>74</v>
@@ -15048,10 +15208,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>392</v>
+        <v>336</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15062,7 +15222,7 @@
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>74</v>
@@ -15074,7 +15234,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>393</v>
+        <v>337</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15127,13 +15287,13 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>392</v>
+        <v>338</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>74</v>
@@ -15147,10 +15307,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>394</v>
+        <v>340</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15161,7 +15321,7 @@
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>74</v>
@@ -15173,7 +15333,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15226,13 +15386,13 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>394</v>
+        <v>342</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>74</v>
@@ -15246,10 +15406,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>396</v>
+        <v>421</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>396</v>
+        <v>344</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15260,7 +15420,7 @@
         <v>80</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>74</v>
@@ -15272,12 +15432,10 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>397</v>
+        <v>345</v>
       </c>
       <c r="L136" s="2"/>
-      <c r="M136" t="s" s="2">
-        <v>398</v>
-      </c>
+      <c r="M136" s="2"/>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -15327,13 +15485,13 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>396</v>
+        <v>346</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>74</v>
@@ -15347,18 +15505,16 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>399</v>
+        <v>348</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E137" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>80</v>
       </c>
@@ -15375,12 +15531,10 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="L137" s="2"/>
-      <c r="M137" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M137" s="2"/>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -15406,11 +15560,13 @@
         <v>74</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y137" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z137" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>74</v>
@@ -15428,7 +15584,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>89</v>
+        <v>350</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15448,10 +15604,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>400</v>
+        <v>352</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15462,7 +15618,7 @@
         <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>74</v>
@@ -15474,12 +15630,10 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>91</v>
+        <v>353</v>
       </c>
       <c r="L138" s="2"/>
-      <c r="M138" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M138" s="2"/>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -15529,13 +15683,13 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>93</v>
+        <v>354</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>74</v>
@@ -15549,10 +15703,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>401</v>
+        <v>356</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15575,12 +15729,10 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>95</v>
+        <v>357</v>
       </c>
       <c r="L139" s="2"/>
-      <c r="M139" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M139" s="2"/>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -15630,7 +15782,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>97</v>
+        <v>358</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -15642,7 +15794,7 @@
         <v>74</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>74</v>
@@ -15650,18 +15802,16 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>402</v>
+        <v>360</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E140" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>80</v>
       </c>
@@ -15678,12 +15828,10 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>85</v>
+        <v>361</v>
       </c>
       <c r="L140" s="2"/>
-      <c r="M140" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M140" s="2"/>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -15709,11 +15857,13 @@
         <v>74</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y140" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z140" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>74</v>
@@ -15731,7 +15881,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>89</v>
+        <v>362</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -15751,18 +15901,16 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>403</v>
+        <v>364</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E141" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>80</v>
       </c>
@@ -15779,12 +15927,10 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>102</v>
+        <v>365</v>
       </c>
       <c r="L141" s="2"/>
-      <c r="M141" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M141" s="2"/>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -15834,7 +15980,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>104</v>
+        <v>366</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -15854,18 +16000,16 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>404</v>
+        <v>368</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E142" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>80</v>
       </c>
@@ -15882,12 +16026,10 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>107</v>
+        <v>369</v>
       </c>
       <c r="L142" s="2"/>
-      <c r="M142" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M142" s="2"/>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -15937,7 +16079,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>109</v>
+        <v>370</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -15957,20 +16099,18 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E143" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>75</v>
@@ -15985,12 +16125,10 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>112</v>
+        <v>373</v>
       </c>
       <c r="L143" s="2"/>
-      <c r="M143" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M143" s="2"/>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -15998,7 +16136,7 @@
       </c>
       <c r="Q143" s="2"/>
       <c r="R143" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S143" t="s" s="2">
         <v>74</v>
@@ -16040,7 +16178,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>115</v>
+        <v>374</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16060,23 +16198,21 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E144" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>74</v>
@@ -16088,12 +16224,10 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>102</v>
+        <v>431</v>
       </c>
       <c r="L144" s="2"/>
-      <c r="M144" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M144" s="2"/>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -16143,13 +16277,13 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>119</v>
+        <v>430</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>74</v>
@@ -16163,10 +16297,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>407</v>
+        <v>432</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16189,12 +16323,10 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>95</v>
+        <v>433</v>
       </c>
       <c r="L145" s="2"/>
-      <c r="M145" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M145" s="2"/>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -16244,7 +16376,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>125</v>
+        <v>432</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16264,10 +16396,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16278,7 +16410,7 @@
         <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>74</v>
@@ -16290,7 +16422,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>85</v>
+        <v>435</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16301,7 +16433,7 @@
       </c>
       <c r="Q146" s="2"/>
       <c r="R146" t="s" s="2">
-        <v>409</v>
+        <v>74</v>
       </c>
       <c r="S146" t="s" s="2">
         <v>74</v>
@@ -16319,11 +16451,13 @@
         <v>74</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y146" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z146" t="s" s="2">
-        <v>410</v>
+        <v>74</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>74</v>
@@ -16341,13 +16475,13 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>74</v>
@@ -16361,10 +16495,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16372,10 +16506,10 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>74</v>
@@ -16387,10 +16521,12 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="L147" s="2"/>
-      <c r="M147" s="2"/>
+      <c r="M147" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -16440,13 +16576,13 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>411</v>
+        <v>436</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>74</v>
@@ -16460,21 +16596,23 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E148" s="2"/>
+      <c r="E148" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>74</v>
@@ -16486,10 +16624,12 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>414</v>
+        <v>85</v>
       </c>
       <c r="L148" s="2"/>
-      <c r="M148" s="2"/>
+      <c r="M148" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -16515,13 +16655,11 @@
         <v>74</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>74</v>
@@ -16539,26 +16677,1137 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>413</v>
+        <v>89</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH148" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="149" hidden="true">
+      <c r="A149" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G149" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI148" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK148" t="s" s="2">
+      <c r="H149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L149" s="2"/>
+      <c r="M149" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N149" s="2"/>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="150" hidden="true">
+      <c r="A150" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L150" s="2"/>
+      <c r="M150" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N150" s="2"/>
+      <c r="O150" s="2"/>
+      <c r="P150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="151" hidden="true">
+      <c r="A151" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E151" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L151" s="2"/>
+      <c r="M151" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
+      <c r="P151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y151" s="2"/>
+      <c r="Z151" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="152" hidden="true">
+      <c r="A152" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E152" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L152" s="2"/>
+      <c r="M152" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N152" s="2"/>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="153" hidden="true">
+      <c r="A153" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E153" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L153" s="2"/>
+      <c r="M153" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="154" hidden="true">
+      <c r="A154" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E154" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F154" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L154" s="2"/>
+      <c r="M154" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="155" hidden="true">
+      <c r="A155" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E155" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F155" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L155" s="2"/>
+      <c r="M155" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N155" s="2"/>
+      <c r="O155" s="2"/>
+      <c r="P155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK155" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="156" hidden="true">
+      <c r="A156" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L156" s="2"/>
+      <c r="M156" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+      <c r="P156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK156" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="157" hidden="true">
+      <c r="A157" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L157" s="2"/>
+      <c r="M157" s="2"/>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
+      <c r="P157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y157" s="2"/>
+      <c r="Z157" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK157" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="158" hidden="true">
+      <c r="A158" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L158" s="2"/>
+      <c r="M158" s="2"/>
+      <c r="N158" s="2"/>
+      <c r="O158" s="2"/>
+      <c r="P158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK158" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="159" hidden="true">
+      <c r="A159" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L159" s="2"/>
+      <c r="M159" s="2"/>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK159" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK148">
+  <autoFilter ref="A1:AK159">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16568,7 +17817,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI147">
+  <conditionalFormatting sqref="A2:AI158">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
